--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:10</t>
+    <t xml:space="preserve">2026-09-09 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:04</t>
+    <t xml:space="preserve">2026-09-17 14:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:01</t>
+    <t xml:space="preserve">2026-09-23 12:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:30</t>
+    <t xml:space="preserve">2026-10-02 14:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:14</t>
+    <t xml:space="preserve">2026-10-05 10:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -605,7 +605,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>977059.62</v>
+        <v>977059.63</v>
       </c>
     </row>
     <row r="5">
@@ -656,7 +656,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>947986.62</v>
+        <v>947986.63</v>
       </c>
     </row>
     <row r="8">
@@ -758,7 +758,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>892700.62</v>
+        <v>892700.63</v>
       </c>
     </row>
     <row r="14">
@@ -1030,7 +1030,7 @@
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>759157.12</v>
+        <v>759157.13</v>
       </c>
     </row>
     <row r="30">
